--- a/parameters/UA/hydrogen/demand_parameters.xlsx
+++ b/parameters/UA/hydrogen/demand_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unioxfordnexus-my.sharepoint.com/personal/engs2859_ox_ac_uk/Documents/Geo-X/Geo-X/parameters/UA/hydrogen/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14108EEA-F5FC-4BFC-9E4A-3332C47324E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{14108EEA-F5FC-4BFC-9E4A-3332C47324E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F01368D-E3A0-294A-AE45-85E0B4A707D7}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
+    <workbookView xWindow="42720" yWindow="600" windowWidth="21600" windowHeight="11300" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand centers" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>Demand state</t>
   </si>
   <si>
-    <t>Zakarpattia</t>
+    <t>Odessa</t>
   </si>
 </sst>
 </file>
@@ -63,8 +63,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
@@ -108,14 +108,14 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -433,16 +433,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21CD761-0C02-5F48-878C-D5E4B46C4E1D}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="41.375" customWidth="1"/>
-    <col min="2" max="2" width="16.375" customWidth="1"/>
-    <col min="3" max="3" width="20.125" customWidth="1"/>
-    <col min="4" max="4" width="22.375" customWidth="1"/>
-    <col min="5" max="5" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="41.33203125" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.33203125" customWidth="1"/>
+    <col min="5" max="5" width="29.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -459,15 +459,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2">
-        <v>48.6</v>
+        <v>46.5</v>
       </c>
       <c r="C2" s="2">
-        <v>22.3</v>
+        <v>30.75</v>
       </c>
       <c r="D2">
         <v>10000000</v>
@@ -476,7 +476,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D7" s="1"/>
     </row>
   </sheetData>
